--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T11:02:30+00:00</t>
+    <t>2023-11-06T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1413,7 +1413,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-bp-measurement-method</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-bp-measurement-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2613,7 +2613,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.76171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="26.1796875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:08:49+00:00</t>
+    <t>2023-11-07T10:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:16:09+00:00</t>
+    <t>2023-11-07T10:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:18:25+00:00</t>
+    <t>2023-11-07T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:25:25+00:00</t>
+    <t>2023-11-07T10:39:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:39:28+00:00</t>
+    <t>2023-11-07T10:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/update-vs-url/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:47:16+00:00</t>
+    <t>2023-11-07T10:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
